--- a/projects/project-3/assignment/src/data/ies-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/ies-axioms.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SubClassOf: Responsible Actor State</t>
+          <t>SubClassOf: Responsible Actor State | SubClassOf: holds Account only Account</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>SubClassOf: Business Event | SubClassOf: Trade Event</t>
+          <t>SubClassOf: Business Event | SubClassOf: Trade Event | SubClassOf: transfer Value only Amount Of Money</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>SubClassOf: Device | SubClassOf: System State</t>
+          <t>SubClassOf: Device | SubClassOf: System State | SubClassOf: radio Coverage only Radio Coverage Area</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>SubClassOf: Actor State</t>
+          <t>SubClassOf: Actor State | SubClassOf: works For only Responsible Actor</t>
         </is>
       </c>
     </row>
